--- a/Xedge/Xedge_20260524.xlsx
+++ b/Xedge/Xedge_20260524.xlsx
@@ -815,7 +815,7 @@
       </c>
       <c r="C2" s="16" t="inlineStr">
         <is>
-          <t>【未経験OK】Webデザイナー◆研修1年・推し活手当あり</t>
+          <t>【未経験OK】研修1年でプロのWebデザイナーへ、推し活手当も</t>
         </is>
       </c>
       <c r="D2" s="16" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="C3" s="7" t="inlineStr">
         <is>
-          <t>【未経験OK】SNSマーケター◆推し活が仕事に・賞与年4回</t>
+          <t>【未経験OK】未経験から半年でSNSマーケターへ、賞与年4回</t>
         </is>
       </c>
       <c r="D3" s="7" t="inlineStr">
@@ -1341,7 +1341,7 @@
 ・推し活手当（一部職種）</t>
         </is>
       </c>
-      <c r="BC3" t="inlineStr">
+      <c r="BC3" s="0" t="inlineStr">
         <is>
           <t>内定まで最短一週間
   応募
@@ -1404,7 +1404,7 @@
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>【未経験OK】動画クリエイター◆企画〜編集まで一気通貫</t>
+          <t>【未経験OK】企画から編集まで一気通貫の動画クリエイター</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
@@ -1639,7 +1639,7 @@
 ・推し活手当（一部職種）</t>
         </is>
       </c>
-      <c r="BC4" t="inlineStr">
+      <c r="BC4" s="0" t="inlineStr">
         <is>
           <t>内定まで最短一週間
   応募
@@ -1690,27 +1690,27 @@
       <c r="BR4" s="7" t="n"/>
     </row>
     <row r="5" ht="23.25" customHeight="1" s="15">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="0" t="inlineStr">
         <is>
           <t>募集中</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="0" t="inlineStr">
         <is>
           <t>株式会社Ｘｅｄｇｅ</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>【未経験OK】出版グラフィックデザイナー◆書籍〜グッズまで</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
+      <c r="C5" s="0" t="inlineStr">
+        <is>
+          <t>【未経験OK】書籍からグッズまで手がける出版デザイナー</t>
+        </is>
+      </c>
+      <c r="D5" s="0" t="inlineStr">
         <is>
           <t>DTPデザイナー</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="0" t="inlineStr">
         <is>
           <t>書籍・雑誌・パッケージ・ライブグッズ──企業の「知」と「世界観」を形にする／DTP基礎マニュアル完備＋先輩の隣指導で安心デビュー／紙＋Web＋動画のハイブリッドキャリアへ／(株)iRupで、形に残る仕事を</t>
         </is>
@@ -1720,74 +1720,74 @@
           <t>1700013</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G5" s="0" t="inlineStr">
         <is>
           <t>東京都 豊島区 東池袋</t>
         </is>
       </c>
       <c r="H5" s="2" t="n"/>
-      <c r="J5" t="inlineStr">
+      <c r="J5" s="0" t="inlineStr">
         <is>
           <t>正社員</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="K5" s="0" t="inlineStr">
         <is>
           <t>いいえ</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="L5" s="0" t="inlineStr">
         <is>
           <t>月給</t>
         </is>
       </c>
-      <c r="M5" t="n">
+      <c r="M5" s="0" t="n">
         <v>250000</v>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="O5" s="0" t="inlineStr">
         <is>
           <t>最低額を表示</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="P5" s="0" t="inlineStr">
         <is>
           <t>なし</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="W5" s="0" t="inlineStr">
         <is>
           <t>固定時間制、シフト制、変形労働時間制</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="X5" s="0" t="inlineStr">
         <is>
           <t>160</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="Z5" s="0" t="inlineStr">
         <is>
           <t>厚生年金、健康保険、雇用保険、労災保険</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AB5" s="0" t="inlineStr">
         <is>
           <t>あり</t>
         </is>
       </c>
-      <c r="AC5" t="n">
+      <c r="AC5" s="0" t="n">
         <v>6</v>
       </c>
-      <c r="AD5" t="inlineStr">
+      <c r="AD5" s="0" t="inlineStr">
         <is>
           <t>ヶ月</t>
         </is>
       </c>
-      <c r="AE5" t="inlineStr">
+      <c r="AE5" s="0" t="inlineStr">
         <is>
           <t>同条件</t>
         </is>
       </c>
-      <c r="AT5" t="inlineStr">
+      <c r="AT5" s="0" t="inlineStr">
         <is>
           <t>「自分の手で形に残るものを作りたい」その想いを、iRupは出版・グラフィックの現場で叶えます。
 未経験からブランドを支えるデザイナーへ──育成体制と多彩な案件で、確かなキャリアを築いていただきます。
@@ -1817,7 +1817,7 @@
 そんな仕事を、iRupで一緒にしませんか。</t>
         </is>
       </c>
-      <c r="AU5" t="inlineStr">
+      <c r="AU5" s="0" t="inlineStr">
         <is>
           <t>未経験から「形に残る仕事」をするための、安心と成長の仕組みを揃えました。
 ◆ 【独自マニュアル完備】DTPの基礎から印刷の仕組みまで体系化
@@ -1834,7 +1834,7 @@
 クリエイターの感性は、休日のインプットで磨かれる。だから、休む文化を制度で守っています。</t>
         </is>
       </c>
-      <c r="AV5" t="inlineStr">
+      <c r="AV5" s="0" t="inlineStr">
         <is>
           <t>「ものを作るのが好き」「形に残る仕事をしたい」──その気持ちが、一番のスタートラインです。
 ◆ 【こんな方を歓迎】未経験・第二新卒・若手の挑戦を応援
@@ -1850,7 +1850,7 @@
 「好き」を仕事に変える一歩を、iRupで踏み出してください。</t>
         </is>
       </c>
-      <c r="AW5" t="inlineStr">
+      <c r="AW5" s="0" t="inlineStr">
         <is>
           <t>【勤務時間例】
   (1)9:00~18:00 （完全土日祝休み）
@@ -1859,7 +1859,7 @@
   フレックス勤務/リモート勤務/シフト制</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
+      <c r="AX5" s="0" t="inlineStr">
         <is>
           <t>完全週休2日制（土日祝休み）
 年間休日125日以上
@@ -1871,18 +1871,18 @@
 ・産前産後休暇／育児休暇（取得率100％）</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr">
+      <c r="AY5" s="0" t="inlineStr">
         <is>
           <t>※プロジェクトにより異なる。
   ご要望を最大限考慮し、案件のご提案をさせていただくスタイルです。</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
+      <c r="AZ5" s="0" t="inlineStr">
         <is>
           <t>※プロジェクトにより異なる。</t>
         </is>
       </c>
-      <c r="BA5" t="inlineStr">
+      <c r="BA5" s="0" t="inlineStr">
         <is>
           <t>月給：25万円〜60万円＋各種手当
   ※経験・スキル・単価に応じて決定
@@ -1896,7 +1896,7 @@
   各種手当（教育手当、役職手当、残業手当）</t>
         </is>
       </c>
-      <c r="BB5" t="inlineStr">
+      <c r="BB5" s="0" t="inlineStr">
         <is>
           <t>・各種社会保険完備（健康保険・厚生年金・雇用保険・労災保険）
 ・定期健康診断
@@ -1910,7 +1910,7 @@
 ・推し活手当（一部職種）</t>
         </is>
       </c>
-      <c r="BC5" t="inlineStr">
+      <c r="BC5" s="0" t="inlineStr">
         <is>
           <t>内定まで最短一週間
   応募
@@ -1922,30 +1922,30 @@
   内定</t>
         </is>
       </c>
-      <c r="BD5" t="inlineStr">
+      <c r="BD5" s="0" t="inlineStr">
         <is>
           <t>05fe0186-23c3-4eca-a50f-a7b4fde44ff6、3b521c27-3d85-4231-8fa0-742b9e5ddc01、e5b13a93-0c7b-43db-983b-69a6fe755bc4、366fd1b8-0326-4853-adc6-2944011a324a、a52f186b-e9f6-4dcf-bff3-0f58abb10151</t>
         </is>
       </c>
-      <c r="BE5" t="inlineStr">
+      <c r="BE5" s="0" t="inlineStr">
         <is>
           <t>交通費支給、在宅OK</t>
         </is>
       </c>
-      <c r="BH5" t="n">
+      <c r="BH5" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="BI5" t="inlineStr">
+      <c r="BI5" s="0" t="inlineStr">
         <is>
           <t>任意</t>
         </is>
       </c>
-      <c r="BJ5" t="inlineStr">
+      <c r="BJ5" s="0" t="inlineStr">
         <is>
           <t>生年月日、電話番号</t>
         </is>
       </c>
-      <c r="BM5" t="inlineStr">
+      <c r="BM5" s="0" t="inlineStr">
         <is>
           <t>recruit@xedge-inc.com</t>
         </is>
@@ -1957,27 +1957,27 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="0" t="inlineStr">
         <is>
           <t>募集中</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="0" t="inlineStr">
         <is>
           <t>株式会社Ｘｅｄｇｅ</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>【未経験可】フルリモートインフラ／保守運用エンジニア</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
+      <c r="C6" s="0" t="inlineStr">
+        <is>
+          <t>【未経験可】フルリモート可能なインフラ／保守運用エンジニア</t>
+        </is>
+      </c>
+      <c r="D6" s="0" t="inlineStr">
         <is>
           <t>データベースエンジニア、保守/運用/サポートエンジニア、QA/テストエンジニア</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" s="0" t="inlineStr">
         <is>
           <t>未経験OK／フルリモート相談可／単価開示で透明な評価／クラウド・DB・保守運用・QAなど領域を選んでスキルアップ／賞与・昇給制度あり／(株)iRupが手厚い研修と先輩エンジニアの伴走でプロデビューまで導きます</t>
         </is>
@@ -1987,7 +1987,7 @@
           <t>4600008</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G6" s="0" t="inlineStr">
         <is>
           <t>愛知県 名古屋市 中区 栄</t>
         </is>
@@ -1997,66 +1997,66 @@
           <t>1-7-25</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J6" s="0" t="inlineStr">
         <is>
           <t>正社員</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="K6" s="0" t="inlineStr">
         <is>
           <t>いいえ</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="L6" s="0" t="inlineStr">
         <is>
           <t>月給</t>
         </is>
       </c>
-      <c r="M6" t="n">
+      <c r="M6" s="0" t="n">
         <v>230000</v>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="O6" s="0" t="inlineStr">
         <is>
           <t>範囲で表示</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="P6" s="0" t="inlineStr">
         <is>
           <t>なし</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="W6" s="0" t="inlineStr">
         <is>
           <t>固定時間制、フレックスタイム制度</t>
         </is>
       </c>
-      <c r="X6" t="n">
+      <c r="X6" s="0" t="n">
         <v>160</v>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="Z6" s="0" t="inlineStr">
         <is>
           <t>厚生年金、健康保険、雇用保険、労災保険</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AB6" s="0" t="inlineStr">
         <is>
           <t>あり</t>
         </is>
       </c>
-      <c r="AC6" t="n">
+      <c r="AC6" s="0" t="n">
         <v>6</v>
       </c>
-      <c r="AD6" t="inlineStr">
+      <c r="AD6" s="0" t="inlineStr">
         <is>
           <t>ヶ月</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr">
+      <c r="AE6" s="0" t="inlineStr">
         <is>
           <t>同条件</t>
         </is>
       </c>
-      <c r="AT6" t="inlineStr">
+      <c r="AT6" s="0" t="inlineStr">
         <is>
           <t>「IT未経験から、手に職をつけたい」その本気を、iRupは透明な制度と育成環境で支えます。
 飲食・販売・事務出身の先輩が多数活躍中──ゼロからプロのエンジニアへ、確かな一歩を踏み出してください。
@@ -2082,7 +2082,7 @@
 iRupで、エンジニアとしての一生モノのキャリアを始めましょう。</t>
         </is>
       </c>
-      <c r="AU6" t="inlineStr">
+      <c r="AU6" s="0" t="inlineStr">
         <is>
           <t>報酬・働き方・学習環境すべてで「未経験から育てる」を本気で実装しました。
 ◆ 【単価開示100％】何で評価されているかが見える
@@ -2099,7 +2099,7 @@
 頑張りを「次の年収」できちんと返す仕組みです。</t>
         </is>
       </c>
-      <c r="AV6" t="inlineStr">
+      <c r="AV6" s="0" t="inlineStr">
         <is>
           <t>「ITに興味がある」「手に職をつけたい」──その気持ちが、何よりも大切なスタートラインです。
 ◆ 【こんな方を歓迎】未経験・第二新卒・異業種出身の挑戦を応援
@@ -2115,7 +2115,7 @@
 意欲とコミュニケーションを重視します。あなたのチャレンジを、iRupは全力で支えます。</t>
         </is>
       </c>
-      <c r="AW6" t="inlineStr">
+      <c r="AW6" s="0" t="inlineStr">
         <is>
           <t>【勤務時間例】
 (1)9:00〜18:00（完全土日祝休み）
@@ -2123,7 +2123,7 @@
 ※プロジェクト先に準ずる。フレックス／リモート／シフトなど、案件に応じて選択可能。</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
+      <c r="AX6" s="0" t="inlineStr">
         <is>
           <t>完全週休2日制（土日祝）
 年間休日125日以上
@@ -2134,18 +2134,18 @@
 ・有給休暇（入社半年後付与）</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr">
+      <c r="AY6" s="0" t="inlineStr">
         <is>
           <t>※プロジェクトにより異なる。
 ご要望を最大限考慮し、案件のご提案をさせていただくスタイルです。</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
+      <c r="AZ6" s="0" t="inlineStr">
         <is>
           <t>※プロジェクトにより異なる。</t>
         </is>
       </c>
-      <c r="BA6" t="inlineStr">
+      <c r="BA6" s="0" t="inlineStr">
         <is>
           <t>月給：23万円〜60万円＋各種手当
 ※経験・スキル・単価に応じて決定
@@ -2161,7 +2161,7 @@
 【各種手当】教育手当／役職手当／残業手当</t>
         </is>
       </c>
-      <c r="BB6" t="inlineStr">
+      <c r="BB6" s="0" t="inlineStr">
         <is>
           <t>・各種社会保険完備（健康保険・厚生年金・雇用保険・労災保険）
 ・定期健康診断
@@ -2173,7 +2173,7 @@
 ・月例食事会（自由参加）</t>
         </is>
       </c>
-      <c r="BC6" t="inlineStr">
+      <c r="BC6" s="0" t="inlineStr">
         <is>
           <t>内定まで最短1週間
 応募
@@ -2185,40 +2185,40 @@
 内定</t>
         </is>
       </c>
-      <c r="BD6" t="inlineStr">
+      <c r="BD6" s="0" t="inlineStr">
         <is>
           <t>05fe0186-23c3-4eca-a50f-a7b4fde44ff6、3b521c27-3d85-4231-8fa0-742b9e5ddc01、e5b13a93-0c7b-43db-983b-69a6fe755bc4、366fd1b8-0326-4853-adc6-2944011a324a、a52f186b-e9f6-4dcf-bff3-0f58abb10151</t>
         </is>
       </c>
-      <c r="BE6" t="inlineStr">
+      <c r="BE6" s="0" t="inlineStr">
         <is>
           <t>在宅あり</t>
         </is>
       </c>
-      <c r="BF6" t="inlineStr">
+      <c r="BF6" s="0" t="inlineStr">
         <is>
           <t>交通費支給</t>
         </is>
       </c>
-      <c r="BG6" t="inlineStr">
+      <c r="BG6" s="0" t="inlineStr">
         <is>
           <t>昇給あり</t>
         </is>
       </c>
-      <c r="BH6" t="n">
+      <c r="BH6" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="BI6" t="inlineStr">
+      <c r="BI6" s="0" t="inlineStr">
         <is>
           <t>任意</t>
         </is>
       </c>
-      <c r="BJ6" t="inlineStr">
+      <c r="BJ6" s="0" t="inlineStr">
         <is>
           <t>生年月日、電話番号</t>
         </is>
       </c>
-      <c r="BM6" t="inlineStr">
+      <c r="BM6" s="0" t="inlineStr">
         <is>
           <t>recruit@xedge-inc.com</t>
         </is>
@@ -2228,7 +2228,7 @@
           <t>080-7442-1232</t>
         </is>
       </c>
-      <c r="BP6" t="inlineStr">
+      <c r="BP6" s="0" t="inlineStr">
         <is>
           <t>利用する</t>
         </is>

--- a/Xedge/Xedge_20260524.xlsx
+++ b/Xedge/Xedge_20260524.xlsx
@@ -877,7 +877,7 @@
       <c r="V2" s="16" t="n"/>
       <c r="W2" s="16" t="inlineStr">
         <is>
-          <t>固定時間制、シフト制、変形労働時間制</t>
+          <t>固定時間制、フレックスタイム制度</t>
         </is>
       </c>
       <c r="X2" s="16" t="inlineStr">
@@ -1019,16 +1019,7 @@
       </c>
       <c r="BA2" s="16" t="inlineStr">
         <is>
-          <t>月給：25万円〜60万円＋各種手当
-  ※経験・スキル・単価に応じて決定
-  ※単価開示100％のため、昇給ロジックが明確
-  【モデル年収】
-  1年目（未経験）：300〜350万円経験
-  2〜3年目：450〜600万円5年目：600万円以上も可能
-  昇給（年2回grade査定）
-  賞与（年4回incentive査定1月4月7月10月）
-  ボーナス（業績ボーナス年1回）
-  各種手当（教育手当、役職手当、残業手当）</t>
+          <t>月給：25万円〜　＋各種手当</t>
         </is>
       </c>
       <c r="BB2" s="16" t="inlineStr">
@@ -1174,7 +1165,7 @@
       <c r="V3" s="7" t="n"/>
       <c r="W3" s="7" t="inlineStr">
         <is>
-          <t>固定時間制、シフト制、変形労働時間制</t>
+          <t>固定時間制、フレックスタイム制度</t>
         </is>
       </c>
       <c r="X3" s="7" t="inlineStr">
@@ -1315,16 +1306,7 @@
       </c>
       <c r="BA3" s="7" t="inlineStr">
         <is>
-          <t>月給：25万円〜60万円＋各種手当
-  ※経験・スキル・単価に応じて決定
-  ※単価開示100％のため、昇給ロジックが明確
-  【モデル年収】
-  1年目（未経験）：300〜350万円経験
-  2〜3年目：450〜600万円5年目：600万円以上も可能
-  昇給（年2回grade査定）
-  賞与（年4回incentive査定1月4月7月10月）
-  ボーナス（業績ボーナス年1回）
-  各種手当（教育手当、役職手当、残業手当）</t>
+          <t>月給：25万円〜　＋各種手当</t>
         </is>
       </c>
       <c r="BB3" s="7" t="inlineStr">
@@ -1470,7 +1452,7 @@
       <c r="V4" s="7" t="n"/>
       <c r="W4" s="7" t="inlineStr">
         <is>
-          <t>固定時間制、シフト制、変形労働時間制</t>
+          <t>固定時間制、フレックスタイム制度</t>
         </is>
       </c>
       <c r="X4" s="7" t="inlineStr">
@@ -1613,16 +1595,7 @@
       </c>
       <c r="BA4" s="7" t="inlineStr">
         <is>
-          <t>月給：25万円〜60万円＋各種手当
-  ※経験・スキル・単価に応じて決定
-  ※単価開示100％のため、昇給ロジックが明確
-  【モデル年収】
-  1年目（未経験）：300〜350万円経験
-  2〜3年目：450〜600万円5年目：600万円以上も可能
-  昇給（年2回grade査定）
-  賞与（年4回incentive査定1月4月7月10月）
-  ボーナス（業績ボーナス年1回）
-  各種手当（教育手当、役職手当、残業手当）</t>
+          <t>月給：23万円〜　＋各種手当</t>
         </is>
       </c>
       <c r="BB4" s="7" t="inlineStr">
@@ -1756,7 +1729,7 @@
       </c>
       <c r="W5" s="0" t="inlineStr">
         <is>
-          <t>固定時間制、シフト制、変形労働時間制</t>
+          <t>固定時間制、フレックスタイム制度</t>
         </is>
       </c>
       <c r="X5" s="0" t="inlineStr">
@@ -1884,16 +1857,7 @@
       </c>
       <c r="BA5" s="0" t="inlineStr">
         <is>
-          <t>月給：25万円〜60万円＋各種手当
-  ※経験・スキル・単価に応じて決定
-  ※単価開示100％のため、昇給ロジックが明確
-  【モデル年収】
-  1年目（未経験）：300〜350万円経験
-  2〜3年目：450〜600万円5年目：600万円以上も可能
-  昇給（年2回grade査定）
-  賞与（年4回incentive査定1月4月7月10月）
-  ボーナス（業績ボーナス年1回）
-  各種手当（教育手当、役職手当、残業手当）</t>
+          <t>月給：25万円〜　＋各種手当</t>
         </is>
       </c>
       <c r="BB5" s="0" t="inlineStr">
@@ -2014,6 +1978,9 @@
       </c>
       <c r="M6" s="0" t="n">
         <v>230000</v>
+      </c>
+      <c r="N6" t="n">
+        <v>500000</v>
       </c>
       <c r="O6" s="0" t="inlineStr">
         <is>
@@ -2147,7 +2114,7 @@
       </c>
       <c r="BA6" s="0" t="inlineStr">
         <is>
-          <t>月給：23万円〜60万円＋各種手当
+          <t>月給：23万円〜50万円＋各種手当
 ※経験・スキル・単価に応じて決定
 ※単価開示100％のため、昇給ロジックが明確
 【モデル年収】

--- a/Xedge/Xedge_20260524.xlsx
+++ b/Xedge/Xedge_20260524.xlsx
@@ -902,7 +902,7 @@
       </c>
       <c r="AD2" s="16" t="inlineStr">
         <is>
-          <t>ヶ月</t>
+          <t>か月</t>
         </is>
       </c>
       <c r="AE2" s="16" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="AD3" s="7" t="inlineStr">
         <is>
-          <t>ヶ月</t>
+          <t>か月</t>
         </is>
       </c>
       <c r="AE3" s="7" t="inlineStr">
@@ -1477,7 +1477,7 @@
       </c>
       <c r="AD4" s="7" t="inlineStr">
         <is>
-          <t>ヶ月</t>
+          <t>か月</t>
         </is>
       </c>
       <c r="AE4" s="7" t="inlineStr">
@@ -1752,7 +1752,7 @@
       </c>
       <c r="AD5" s="0" t="inlineStr">
         <is>
-          <t>ヶ月</t>
+          <t>か月</t>
         </is>
       </c>
       <c r="AE5" s="0" t="inlineStr">
@@ -1979,7 +1979,7 @@
       <c r="M6" s="0" t="n">
         <v>230000</v>
       </c>
-      <c r="N6" t="n">
+      <c r="N6" s="0" t="n">
         <v>500000</v>
       </c>
       <c r="O6" s="0" t="inlineStr">
@@ -2015,7 +2015,7 @@
       </c>
       <c r="AD6" s="0" t="inlineStr">
         <is>
-          <t>ヶ月</t>
+          <t>か月</t>
         </is>
       </c>
       <c r="AE6" s="0" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="BE6" s="0" t="inlineStr">
         <is>
-          <t>在宅あり</t>
+          <t>在宅OK</t>
         </is>
       </c>
       <c r="BF6" s="0" t="inlineStr">
@@ -2169,7 +2169,7 @@
       </c>
       <c r="BG6" s="0" t="inlineStr">
         <is>
-          <t>昇給あり</t>
+          <t>昇給・昇格あり</t>
         </is>
       </c>
       <c r="BH6" s="0" t="n">
